--- a/contractor_forms/023_supplier_accreditation_registration_form_template--contractor_forms.xlsx
+++ b/contractor_forms/023_supplier_accreditation_registration_form_template--contractor_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -865,8 +865,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -894,12 +894,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'alabama'}</t>
+          <t>alabama</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Alabama'}</t>
+          <t>Alabama</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'alaska'}</t>
+          <t>alaska</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Alaska'}</t>
+          <t>Alaska</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'arizona'}</t>
+          <t>arizona</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Arizona'}</t>
+          <t>Arizona</t>
         </is>
       </c>
     </row>
@@ -945,12 +945,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'arkansas'}</t>
+          <t>arkansas</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Arkansas'}</t>
+          <t>Arkansas</t>
         </is>
       </c>
     </row>
@@ -962,12 +962,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'california'}</t>
+          <t>california</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'California'}</t>
+          <t>California</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'colorado'}</t>
+          <t>colorado</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Colorado'}</t>
+          <t>Colorado</t>
         </is>
       </c>
     </row>
@@ -996,12 +996,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'connecticut'}</t>
+          <t>connecticut</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'Connecticut'}</t>
+          <t>Connecticut</t>
         </is>
       </c>
     </row>
@@ -1013,12 +1013,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_8,_'label':_'delaware'}</t>
+          <t>delaware</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 8, 'label': 'Delaware'}</t>
+          <t>Delaware</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_9,_'label':_'florida'}</t>
+          <t>florida</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 9, 'label': 'Florida'}</t>
+          <t>Florida</t>
         </is>
       </c>
     </row>
@@ -1047,12 +1047,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_10,_'label':_'georgia'}</t>
+          <t>georgia</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 10, 'label': 'Georgia'}</t>
+          <t>Georgia</t>
         </is>
       </c>
     </row>
@@ -1064,12 +1064,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_11,_'label':_'hawaii'}</t>
+          <t>hawaii</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 11, 'label': 'Hawaii'}</t>
+          <t>Hawaii</t>
         </is>
       </c>
     </row>
@@ -1081,12 +1081,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_12,_'label':_'idaho'}</t>
+          <t>idaho</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 12, 'label': 'Idaho'}</t>
+          <t>Idaho</t>
         </is>
       </c>
     </row>
@@ -1098,12 +1098,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_13,_'label':_'illinois'}</t>
+          <t>illinois</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 13, 'label': 'Illinois'}</t>
+          <t>Illinois</t>
         </is>
       </c>
     </row>
@@ -1115,12 +1115,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_14,_'label':_'indiana'}</t>
+          <t>indiana</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 14, 'label': 'Indiana'}</t>
+          <t>Indiana</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_15,_'label':_'iowa'}</t>
+          <t>iowa</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 15, 'label': 'Iowa'}</t>
+          <t>Iowa</t>
         </is>
       </c>
     </row>
@@ -1149,12 +1149,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_16,_'label':_'kansas'}</t>
+          <t>kansas</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 16, 'label': 'Kansas'}</t>
+          <t>Kansas</t>
         </is>
       </c>
     </row>
@@ -1166,12 +1166,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_17,_'label':_'kentucky'}</t>
+          <t>kentucky</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 17, 'label': 'Kentucky'}</t>
+          <t>Kentucky</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_18,_'label':_'louisiana'}</t>
+          <t>louisiana</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 18, 'label': 'Louisiana'}</t>
+          <t>Louisiana</t>
         </is>
       </c>
     </row>
@@ -1200,12 +1200,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_19,_'label':_'maine'}</t>
+          <t>maine</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 19, 'label': 'Maine'}</t>
+          <t>Maine</t>
         </is>
       </c>
     </row>
@@ -1217,12 +1217,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_20,_'label':_'maryland'}</t>
+          <t>maryland</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 20, 'label': 'Maryland'}</t>
+          <t>Maryland</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_21,_'label':_'massachusetts'}</t>
+          <t>massachusetts</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 21, 'label': 'Massachusetts'}</t>
+          <t>Massachusetts</t>
         </is>
       </c>
     </row>
@@ -1251,12 +1251,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_22,_'label':_'michigan'}</t>
+          <t>michigan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 22, 'label': 'Michigan'}</t>
+          <t>Michigan</t>
         </is>
       </c>
     </row>
@@ -1268,12 +1268,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_23,_'label':_'minnesota'}</t>
+          <t>minnesota</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 23, 'label': 'Minnesota'}</t>
+          <t>Minnesota</t>
         </is>
       </c>
     </row>
@@ -1285,12 +1285,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_24,_'label':_'mississippi'}</t>
+          <t>mississippi</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 24, 'label': 'Mississippi'}</t>
+          <t>Mississippi</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_25,_'label':_'missouri'}</t>
+          <t>missouri</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 25, 'label': 'Missouri'}</t>
+          <t>Missouri</t>
         </is>
       </c>
     </row>
@@ -1319,12 +1319,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'service'}</t>
+          <t>service</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Service'}</t>
+          <t>Service</t>
         </is>
       </c>
     </row>
@@ -1336,12 +1336,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'product'}</t>
+          <t>product</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Product'}</t>
+          <t>Product</t>
         </is>
       </c>
     </row>
@@ -1353,12 +1353,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1370,12 +1370,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1387,12 +1387,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1404,12 +1404,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'accredited'}</t>
+          <t>accredited</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Accredited'}</t>
+          <t>Accredited</t>
         </is>
       </c>
     </row>
@@ -1421,12 +1421,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'denied'}</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Denied'}</t>
+          <t>Denied</t>
         </is>
       </c>
     </row>
